--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487112_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487112_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.5853</v>
+        <v>7.7846</v>
       </c>
       <c r="E2" t="n">
-        <v>7.0897</v>
+        <v>7.2087</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4956</v>
+        <v>0.5759</v>
       </c>
       <c r="G2" t="n">
         <v>4.0269</v>
@@ -610,13 +610,13 @@
         <v>2.5091</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7211</v>
+        <v>0.9204</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5473</v>
+        <v>0.6663</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1738</v>
+        <v>0.2541</v>
       </c>
       <c r="V2" t="n">
         <v>0.3281</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. QUINCY-JONES</t>
+          <t>D. CONTRERAS MARTINEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.5897</v>
+        <v>5.7799</v>
       </c>
       <c r="E3" t="n">
-        <v>4.8265</v>
+        <v>2.3272</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7632</v>
+        <v>3.4527</v>
       </c>
       <c r="G3" t="n">
-        <v>3.9012</v>
+        <v>4.2069</v>
       </c>
       <c r="H3" t="n">
-        <v>2.309</v>
+        <v>0.2184</v>
       </c>
       <c r="I3" t="n">
-        <v>1.5923</v>
+        <v>3.9885</v>
       </c>
       <c r="J3" t="n">
-        <v>4.9888</v>
+        <v>4.2933</v>
       </c>
       <c r="K3" t="n">
-        <v>3.6378</v>
+        <v>1.0866</v>
       </c>
       <c r="L3" t="n">
-        <v>1.3509</v>
+        <v>3.2067</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.0875</v>
+        <v>-0.0864</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.3288</v>
+        <v>-0.8682</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2413</v>
+        <v>0.7818000000000001</v>
       </c>
       <c r="P3" t="n">
-        <v>1.7371</v>
+        <v>0.193</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.965</v>
+        <v>-2.8951</v>
       </c>
       <c r="R3" t="n">
-        <v>2.7021</v>
+        <v>3.0881</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2373</v>
+        <v>-0.1338</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5169</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2796</v>
+        <v>-0.2053</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.2859</v>
+        <v>1.5138</v>
       </c>
       <c r="W3" t="n">
-        <v>0.2859</v>
+        <v>0.8576</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.5717</v>
+        <v>0.6562</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. CONTRERAS MARTINEZ</t>
+          <t>A. QUINCY-JONES</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.186</v>
+        <v>5.215</v>
       </c>
       <c r="E4" t="n">
-        <v>1.8671</v>
+        <v>4.5856</v>
       </c>
       <c r="F4" t="n">
-        <v>3.3188</v>
+        <v>0.6294</v>
       </c>
       <c r="G4" t="n">
-        <v>4.2069</v>
+        <v>3.9012</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2184</v>
+        <v>2.309</v>
       </c>
       <c r="I4" t="n">
-        <v>3.9885</v>
+        <v>1.5923</v>
       </c>
       <c r="J4" t="n">
-        <v>4.2933</v>
+        <v>4.9888</v>
       </c>
       <c r="K4" t="n">
-        <v>1.0866</v>
+        <v>3.6378</v>
       </c>
       <c r="L4" t="n">
-        <v>3.2067</v>
+        <v>1.3509</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.0864</v>
+        <v>-1.0875</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.8682</v>
+        <v>-1.3288</v>
       </c>
       <c r="O4" t="n">
-        <v>0.7818000000000001</v>
+        <v>0.2413</v>
       </c>
       <c r="P4" t="n">
-        <v>0.193</v>
+        <v>1.7371</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.8951</v>
+        <v>-0.965</v>
       </c>
       <c r="R4" t="n">
-        <v>3.0881</v>
+        <v>2.7021</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.7277</v>
+        <v>-0.1375</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3886</v>
+        <v>0.276</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3391</v>
+        <v>-0.4135</v>
       </c>
       <c r="V4" t="n">
-        <v>1.5138</v>
+        <v>-0.2859</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8576</v>
+        <v>0.2859</v>
       </c>
       <c r="X4" t="n">
-        <v>0.6562</v>
+        <v>-0.5717</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.357</v>
+        <v>4.6891</v>
       </c>
       <c r="E5" t="n">
-        <v>1.4316</v>
+        <v>1.9511</v>
       </c>
       <c r="F5" t="n">
-        <v>2.9254</v>
+        <v>2.738</v>
       </c>
       <c r="G5" t="n">
         <v>1.9903</v>
@@ -844,13 +844,13 @@
         <v>3.0881</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4356</v>
+        <v>-0.1035</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8183</v>
+        <v>-0.2987</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3827</v>
+        <v>0.1953</v>
       </c>
       <c r="V5" t="n">
         <v>-0.2859</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.2984</v>
+        <v>4.0787</v>
       </c>
       <c r="E6" t="n">
-        <v>2.4088</v>
+        <v>3.0285</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8895999999999999</v>
+        <v>1.0502</v>
       </c>
       <c r="G6" t="n">
         <v>2.9447</v>
@@ -922,13 +922,13 @@
         <v>3.0881</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.1554</v>
+        <v>-0.3751</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4772</v>
+        <v>0.1425</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.6782</v>
+        <v>-0.5175999999999999</v>
       </c>
       <c r="V6" t="n">
         <v>-0.614</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. TRUEBA TAMAYO</t>
+          <t>E. GANDARILLAS GARMENDIA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6986</v>
+        <v>0.9298</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.1323</v>
+        <v>1.1555</v>
       </c>
       <c r="F7" t="n">
-        <v>1.8308</v>
+        <v>-0.2257</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.0939</v>
+        <v>-0.5435</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.3734</v>
+        <v>0.4347</v>
       </c>
       <c r="I7" t="n">
-        <v>1.2795</v>
+        <v>-0.9782</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.0338</v>
+        <v>0.6239</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.6521</v>
+        <v>1.1694</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6183999999999999</v>
+        <v>-0.5455</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.0601</v>
+        <v>-1.1674</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.7213000000000001</v>
+        <v>-0.7347</v>
       </c>
       <c r="O7" t="n">
-        <v>0.6612</v>
+        <v>-0.4327</v>
       </c>
       <c r="P7" t="n">
-        <v>-0</v>
+        <v>1.3511</v>
       </c>
       <c r="Q7" t="n">
         <v>-0.965</v>
       </c>
       <c r="R7" t="n">
-        <v>0.965</v>
+        <v>2.3161</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1785</v>
+        <v>-0.1636</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0912</v>
+        <v>-0.0172</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2697</v>
+        <v>-0.1464</v>
       </c>
       <c r="V7" t="n">
-        <v>0.614</v>
+        <v>0.2859</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.0422</v>
+        <v>1.5138</v>
       </c>
       <c r="X7" t="n">
-        <v>0.6562</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. GOMEZ MERODIO</t>
+          <t>M. CARCOBA BEDIA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4275</v>
+        <v>0.7455000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4025</v>
+        <v>-1.3046</v>
       </c>
       <c r="F8" t="n">
-        <v>0.025</v>
+        <v>2.05</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.0952</v>
+        <v>-0.3708</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.2626</v>
+        <v>1.0422</v>
       </c>
       <c r="I8" t="n">
-        <v>1.1674</v>
+        <v>-1.413</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.9487</v>
+        <v>0.5832000000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.8684</v>
+        <v>1.837</v>
       </c>
       <c r="L8" t="n">
-        <v>0.9197</v>
+        <v>-1.2538</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.1464</v>
+        <v>-0.954</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3942</v>
+        <v>-0.7948</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2478</v>
+        <v>-0.1592</v>
       </c>
       <c r="P8" t="n">
-        <v>1.5441</v>
+        <v>0.579</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.965</v>
+        <v>-1.9301</v>
       </c>
       <c r="R8" t="n">
         <v>2.5091</v>
       </c>
       <c r="S8" t="n">
-        <v>2.519</v>
+        <v>-0.119</v>
       </c>
       <c r="T8" t="n">
-        <v>2.4008</v>
+        <v>0.0423</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1183</v>
+        <v>-0.1613</v>
       </c>
       <c r="V8" t="n">
-        <v>-2.5404</v>
+        <v>0.6562</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.08450000000000001</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.4559</v>
+        <v>0.6562</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. CARCOBA BEDIA</t>
+          <t>D. TRUEBA TAMAYO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1189</v>
+        <v>0.6311</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.8241</v>
+        <v>-0.9320000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>1.943</v>
+        <v>1.5631</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.3708</v>
+        <v>-0.0939</v>
       </c>
       <c r="H9" t="n">
-        <v>1.0422</v>
+        <v>-1.3734</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.413</v>
+        <v>1.2795</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5832000000000001</v>
+        <v>-0.0338</v>
       </c>
       <c r="K9" t="n">
-        <v>1.837</v>
+        <v>-0.6521</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.2538</v>
+        <v>0.6183999999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.954</v>
+        <v>-0.0601</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.7948</v>
+        <v>-0.7213000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.1592</v>
+        <v>0.6612</v>
       </c>
       <c r="P9" t="n">
-        <v>0.579</v>
+        <v>-0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.9301</v>
+        <v>-0.965</v>
       </c>
       <c r="R9" t="n">
-        <v>2.5091</v>
+        <v>0.965</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7456</v>
+        <v>0.111</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4772</v>
+        <v>0.1091</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2684</v>
+        <v>0.002</v>
       </c>
       <c r="V9" t="n">
-        <v>0.6562</v>
+        <v>0.614</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>-0.0422</v>
       </c>
       <c r="X9" t="n">
         <v>0.6562</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>E. GANDARILLAS GARMENDIA</t>
+          <t>J. GOMEZ MERODIO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1158</v>
+        <v>-1.142</v>
       </c>
       <c r="E10" t="n">
-        <v>0.636</v>
+        <v>-1.1402</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.5202</v>
+        <v>-0.0018</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.5435</v>
+        <v>-1.0952</v>
       </c>
       <c r="H10" t="n">
-        <v>0.4347</v>
+        <v>-2.2626</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.9782</v>
+        <v>1.1674</v>
       </c>
       <c r="J10" t="n">
-        <v>0.6239</v>
+        <v>-0.9487</v>
       </c>
       <c r="K10" t="n">
-        <v>1.1694</v>
+        <v>-1.8684</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.5455</v>
+        <v>0.9197</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.1674</v>
+        <v>-0.1464</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.7347</v>
+        <v>-0.3942</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.4327</v>
+        <v>0.2478</v>
       </c>
       <c r="P10" t="n">
-        <v>1.3511</v>
+        <v>1.5441</v>
       </c>
       <c r="Q10" t="n">
         <v>-0.965</v>
       </c>
       <c r="R10" t="n">
-        <v>2.3161</v>
+        <v>2.5091</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.9776</v>
+        <v>0.9495</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5367</v>
+        <v>0.858</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4409</v>
+        <v>0.0915</v>
       </c>
       <c r="V10" t="n">
-        <v>0.2859</v>
+        <v>-2.5404</v>
       </c>
       <c r="W10" t="n">
-        <v>1.5138</v>
+        <v>-0.08450000000000001</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.228</v>
+        <v>-2.4559</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S. MARTINEZ FERNANDEZ</t>
+          <t>J. SANCHEZ MARROYO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.2731</v>
+        <v>-2.0338</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.6084</v>
+        <v>-1.8829</v>
       </c>
       <c r="F11" t="n">
-        <v>1.3353</v>
+        <v>-0.1509</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.4766</v>
+        <v>-1.3765</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.0235</v>
+        <v>-0.6096</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5469000000000001</v>
+        <v>-0.7669</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.4636</v>
+        <v>-0.9426</v>
       </c>
       <c r="K11" t="n">
-        <v>-2.1634</v>
+        <v>-0.3157</v>
       </c>
       <c r="L11" t="n">
-        <v>0.6998</v>
+        <v>-0.6269</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.0129</v>
+        <v>-0.4338</v>
       </c>
       <c r="N11" t="n">
-        <v>0.1399</v>
+        <v>-0.2939</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.1528</v>
+        <v>-0.14</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.579</v>
+        <v>-0.965</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.8951</v>
+        <v>-0.965</v>
       </c>
       <c r="R11" t="n">
-        <v>2.3161</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>1.9526</v>
+        <v>0.3077</v>
       </c>
       <c r="T11" t="n">
-        <v>1.4066</v>
+        <v>0.0248</v>
       </c>
       <c r="U11" t="n">
-        <v>0.5459000000000001</v>
+        <v>0.2829</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.1701</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.6562</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.5138</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. SANCHEZ MARROYO</t>
+          <t>S. MARTINEZ FERNANDEZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.4274</v>
+        <v>-3.1089</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.3836</v>
+        <v>-4.3907</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.0439</v>
+        <v>1.2817</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.3765</v>
+        <v>-1.4766</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.6096</v>
+        <v>-2.0235</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.7669</v>
+        <v>0.5469000000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.9426</v>
+        <v>-1.4636</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.3157</v>
+        <v>-2.1634</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.6269</v>
+        <v>0.6998</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.4338</v>
+        <v>-0.0129</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.2939</v>
+        <v>0.1399</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.14</v>
+        <v>-0.1528</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.965</v>
+        <v>-0.579</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.965</v>
+        <v>-2.8951</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>2.3161</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0859</v>
+        <v>1.1167</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4759</v>
+        <v>0.6243</v>
       </c>
       <c r="U12" t="n">
-        <v>0.39</v>
+        <v>0.4924</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>-2.1701</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>-0.6562</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-1.5138</v>
       </c>
     </row>
     <row r="13">
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>22.6767</v>
+        <v>23.569</v>
       </c>
       <c r="E13" t="n">
-        <v>9.713800000000001</v>
+        <v>10.6062</v>
       </c>
       <c r="F13" t="n">
         <v>12.9626</v>
@@ -1456,7 +1456,7 @@
         <v>-5.9448</v>
       </c>
       <c r="O13" t="n">
-        <v>0.4426000000000002</v>
+        <v>0.4426</v>
       </c>
       <c r="P13" t="n">
         <v>11.5806</v>
@@ -1468,13 +1468,13 @@
         <v>25.0909</v>
       </c>
       <c r="S13" t="n">
-        <v>1.4807</v>
+        <v>2.3728</v>
       </c>
       <c r="T13" t="n">
-        <v>1.6065</v>
+        <v>2.4988</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1258</v>
+        <v>-0.1258999999999998</v>
       </c>
       <c r="V13" t="n">
         <v>-2.4983</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.5011</v>
+        <v>1.7417</v>
       </c>
       <c r="E14" t="n">
         <v>3.0524</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.5513</v>
+        <v>-1.3107</v>
       </c>
       <c r="G14" t="n">
         <v>-1.4909</v>
@@ -1546,13 +1546,13 @@
         <v>0.772</v>
       </c>
       <c r="S14" t="n">
-        <v>0.2935</v>
+        <v>0.5341</v>
       </c>
       <c r="T14" t="n">
         <v>0.5328000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2393</v>
+        <v>0.0013</v>
       </c>
       <c r="V14" t="n">
         <v>1.9264</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.253</v>
+        <v>1.0339</v>
       </c>
       <c r="E15" t="n">
-        <v>0.4528</v>
+        <v>0.7532</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.1998</v>
+        <v>0.2807</v>
       </c>
       <c r="G15" t="n">
         <v>0.07920000000000001</v>
@@ -1624,13 +1624,13 @@
         <v>2.1231</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.2665</v>
+        <v>-0.4855</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.8341</v>
+        <v>-0.5337</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4323</v>
+        <v>0.0482</v>
       </c>
       <c r="V15" t="n">
         <v>2.2123</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. DIAGNE</t>
+          <t>L. SANCHEZ TURRION</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1443</v>
+        <v>-0.1777</v>
       </c>
       <c r="E16" t="n">
-        <v>0.4806</v>
+        <v>1.1144</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.6249</v>
+        <v>-1.2922</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.8522</v>
+        <v>-0.1923</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.825</v>
+        <v>1.2679</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.0272</v>
+        <v>-1.4602</v>
       </c>
       <c r="J16" t="n">
-        <v>1.4902</v>
+        <v>1.6759</v>
       </c>
       <c r="K16" t="n">
-        <v>1.2053</v>
+        <v>1.6352</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2849</v>
+        <v>0.0407</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.3424</v>
+        <v>-1.8682</v>
       </c>
       <c r="N16" t="n">
-        <v>-2.0303</v>
+        <v>-0.3674</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.3121</v>
+        <v>-1.5009</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.158</v>
+        <v>-0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.8951</v>
+        <v>-0.965</v>
       </c>
       <c r="R16" t="n">
-        <v>1.7371</v>
+        <v>0.965</v>
       </c>
       <c r="S16" t="n">
-        <v>0.7224</v>
+        <v>0.3004</v>
       </c>
       <c r="T16" t="n">
-        <v>0.4561</v>
+        <v>0.4035</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2663</v>
+        <v>-0.1031</v>
       </c>
       <c r="V16" t="n">
-        <v>1.1435</v>
+        <v>-0.2859</v>
       </c>
       <c r="W16" t="n">
-        <v>1.4293</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
         <v>-0.2859</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>L. SANCHEZ TURRION</t>
+          <t>M. DIAGNE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2111</v>
+        <v>-0.3984</v>
       </c>
       <c r="E17" t="n">
-        <v>1.2146</v>
+        <v>-0.1202</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.4257</v>
+        <v>-0.2782</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.1923</v>
+        <v>-0.8522</v>
       </c>
       <c r="H17" t="n">
-        <v>1.2679</v>
+        <v>-0.825</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.4602</v>
+        <v>-0.0272</v>
       </c>
       <c r="J17" t="n">
-        <v>1.6759</v>
+        <v>1.4902</v>
       </c>
       <c r="K17" t="n">
-        <v>1.6352</v>
+        <v>1.2053</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0407</v>
+        <v>0.2849</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.8682</v>
+        <v>-2.3424</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.3674</v>
+        <v>-2.0303</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.5009</v>
+        <v>-0.3121</v>
       </c>
       <c r="P17" t="n">
-        <v>-0</v>
+        <v>-1.158</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.965</v>
+        <v>-2.8951</v>
       </c>
       <c r="R17" t="n">
-        <v>0.965</v>
+        <v>1.7371</v>
       </c>
       <c r="S17" t="n">
-        <v>0.267</v>
+        <v>0.4683</v>
       </c>
       <c r="T17" t="n">
-        <v>0.5037</v>
+        <v>-0.1447</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2366</v>
+        <v>0.613</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.2859</v>
+        <v>1.1435</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.4293</v>
       </c>
       <c r="X17" t="n">
         <v>-0.2859</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.9229000000000001</v>
+        <v>-0.9764</v>
       </c>
       <c r="E18" t="n">
         <v>0.4778</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.4006</v>
+        <v>-1.4542</v>
       </c>
       <c r="G18" t="n">
         <v>0.1478</v>
@@ -1858,13 +1858,13 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1573</v>
+        <v>0.1038</v>
       </c>
       <c r="T18" t="n">
         <v>-0.1639</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3212</v>
+        <v>0.2677</v>
       </c>
       <c r="V18" t="n">
         <v>-1.228</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.5415</v>
+        <v>-2.0405</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.5414</v>
+        <v>-1.4412</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.0001</v>
+        <v>-0.5992</v>
       </c>
       <c r="G19" t="n">
         <v>-3.0449</v>
@@ -1936,13 +1936,13 @@
         <v>1.3511</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1633</v>
+        <v>0.6643</v>
       </c>
       <c r="T19" t="n">
-        <v>0.3543</v>
+        <v>0.4545</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.191</v>
+        <v>0.2098</v>
       </c>
       <c r="V19" t="n">
         <v>1.8842</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.5953</v>
+        <v>-2.7535</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.5489</v>
+        <v>-2.3486</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.0464</v>
+        <v>-0.4049</v>
       </c>
       <c r="G20" t="n">
         <v>-0.4278</v>
@@ -2014,13 +2014,13 @@
         <v>1.158</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.1904</v>
+        <v>-0.3487</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5063</v>
+        <v>-0.306</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.6841</v>
+        <v>-0.0427</v>
       </c>
       <c r="V20" t="n">
         <v>-2.1701</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.729</v>
+        <v>-3.0145</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.0941</v>
+        <v>-3.9939</v>
       </c>
       <c r="F21" t="n">
-        <v>0.365</v>
+        <v>0.9794</v>
       </c>
       <c r="G21" t="n">
         <v>-0.6883</v>
@@ -2092,13 +2092,13 @@
         <v>1.7371</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.9406</v>
+        <v>-0.2261</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2406</v>
+        <v>-0.1404</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.7</v>
+        <v>-0.0856</v>
       </c>
       <c r="V21" t="n">
         <v>-0.9421</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.3616</v>
+        <v>-5.6227</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.575</v>
+        <v>-4.6752</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.7865</v>
+        <v>-0.9475</v>
       </c>
       <c r="G22" t="n">
         <v>-2.3514</v>
@@ -2170,13 +2170,13 @@
         <v>1.5441</v>
       </c>
       <c r="S22" t="n">
-        <v>0.622</v>
+        <v>0.3609</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1164</v>
+        <v>0.0162</v>
       </c>
       <c r="U22" t="n">
-        <v>0.5056</v>
+        <v>0.3447</v>
       </c>
       <c r="V22" t="n">
         <v>0.614</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-7.925</v>
+        <v>-7.1305</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.8814</v>
+        <v>-5.7812</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.0436</v>
+        <v>-1.3492</v>
       </c>
       <c r="G23" t="n">
         <v>-3.2929</v>
@@ -2248,13 +2248,13 @@
         <v>2.1231</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.3087</v>
+        <v>0.4858</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0925</v>
+        <v>0.0076</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2162</v>
+        <v>0.4782</v>
       </c>
       <c r="V23" t="n">
         <v>-0.6562</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-22.6766</v>
+        <v>-19.3386</v>
       </c>
       <c r="E24" t="n">
-        <v>-12.9626</v>
+        <v>-12.9625</v>
       </c>
       <c r="F24" t="n">
-        <v>-9.713900000000001</v>
+        <v>-6.375999999999999</v>
       </c>
       <c r="G24" t="n">
         <v>-12.1137</v>
@@ -2326,13 +2326,13 @@
         <v>13.5106</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.4807</v>
+        <v>1.8573</v>
       </c>
       <c r="T24" t="n">
         <v>0.1259000000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.6064</v>
+        <v>1.7315</v>
       </c>
       <c r="V24" t="n">
         <v>2.4981</v>
